--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>69681249.68000001</v>
+        <v>78828</v>
       </c>
     </row>
     <row r="3">
@@ -630,11 +630,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>342809999.7</v>
+        <v>387809.16</v>
       </c>
     </row>
     <row r="4">
@@ -691,11 +691,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>40760998.6</v>
+        <v>46111.52</v>
       </c>
     </row>
     <row r="5">
@@ -752,11 +752,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>25907490</v>
+        <v>29308.25</v>
       </c>
     </row>
     <row r="6">
@@ -813,11 +813,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21052766</v>
+        <v>23816.27</v>
       </c>
     </row>
     <row r="7">
@@ -874,11 +874,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>33762690.71</v>
+        <v>38194.57</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>34280999.97</v>
+        <v>38780.92</v>
       </c>
     </row>
     <row r="9">
@@ -996,11 +996,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>62954998.4</v>
+        <v>71218.82000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1057,11 +1057,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>19148699.36</v>
+        <v>21662.27</v>
       </c>
     </row>
     <row r="11">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>110393325</v>
+        <v>124884.17</v>
       </c>
     </row>
     <row r="12">
@@ -1183,11 +1183,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31220999.46</v>
+        <v>35319.24</v>
       </c>
     </row>
     <row r="13">
@@ -1244,11 +1244,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>32387040</v>
+        <v>36638.34</v>
       </c>
     </row>
     <row r="14">
@@ -1305,11 +1305,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>18945990</v>
+        <v>21432.95</v>
       </c>
     </row>
     <row r="15">
@@ -1366,11 +1366,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>41490000</v>
+        <v>46936.21</v>
       </c>
     </row>
     <row r="16">
@@ -1427,11 +1427,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23910799.71</v>
+        <v>27049.47</v>
       </c>
     </row>
     <row r="17">
@@ -1488,11 +1488,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>36117452</v>
+        <v>40858.43</v>
       </c>
     </row>
     <row r="18">
@@ -1549,11 +1549,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>23390999.38</v>
+        <v>26461.43</v>
       </c>
     </row>
     <row r="19">
@@ -1610,11 +1610,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>51215105.76</v>
+        <v>57937.89</v>
       </c>
     </row>
     <row r="20">
@@ -1671,11 +1671,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>32387040</v>
+        <v>36638.34</v>
       </c>
     </row>
     <row r="21">
@@ -1732,11 +1732,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>30191490</v>
+        <v>34154.59</v>
       </c>
     </row>
   </sheetData>
